--- a/stories/arbres/ATOM-SOC.ARG.002-02.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya marche au marché avec papa. Elle sent le pain chaud. Les étals sont colorés. Elle voit un moulinet. Maya a envie. L'argent se range. Il est dans la poche de papa. Papa est l'adulte. Maya dit : je peux demander. Elle demande à papa. Papa écoute. Parce qu'elle a demandé, papa peut répondre. Papa dit : aujourd'hui, le pain. Le moulinet attend. Maya hoche la tête. Elle tient la main de papa. Ils achètent le pain. Le pain est chaud. Maya dit merci. Demander à l'adulte, c'est la règle.</t>
+          <t>Maya marche au marché avec papa. Elle sent le pain chaud. Les étals sont colorés. Elle voit un moulinet. Maya a envie. L'argent se range. Il est dans la poche de papa. Papa est l'adulte. Je peux demander. Elle demande à papa. Papa écoute. Parce qu'elle a demandé, papa peut répondre. Aujourd'hui, le pain. Le moulinet attend. Maya hoche la tête. Elle tient la main de papa. Ils achètent le pain. Le pain est chaud. Maya dit merci. Demander à l'adulte, c'est la règle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maya marche au marché avec papa. Elle sent le pain chaud. Les étals sont colorés. Elle voit un moulinet. Maya a envie. L'argent se range. Il est dans la poche de papa. Papa est l'adulte.
+enfant-f|Je peux demander. Elle demande à papa. Papa écoute. Parce qu'elle a demandé, papa peut répondre.
+papa|Aujourd'hui, le pain.
+narrateur|Le moulinet attend. Maya hoche la tête. Elle tient la main de papa. Ils achètent le pain. Le pain est chaud. Maya dit merci. Demander à l'adulte, c'est la règle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maya veut un moulinet. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a su demander. Papa, l'adulte, a écouté. L'argent est resté rangé.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maya porte le pain. Papa tient sa main. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-02.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,11 @@
 narrateur|Le moulinet attend. Maya hoche la tête. Elle tient la main de papa. Ils achètent le pain. Le pain est chaud. Maya dit merci. Demander à l'adulte, c'est la règle.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1506,7 @@
           <t>narrateur|Maya veut un moulinet. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1678,7 @@
           <t>narrateur|Maya a su demander. Papa, l'adulte, a écouté. L'argent est resté rangé.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1846,7 @@
           <t>narrateur|Maya porte le pain. Papa tient sa main. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.ARG.002-02.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maya demande pour un achat</t>
+          <t>Le sifflet de bois d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut un sifflet en bois au kiosque. Le sifflet peint n'est plus là. Il tend la main. Papa attend. Amir demande. Le bois est à lui.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya marche au marché avec papa. Elle sent le pain chaud. Les étals sont colorés. Elle voit un moulinet. Maya a envie. L'argent se range. Il est dans la poche de papa. Papa est l'adulte. Je peux demander. Elle demande à papa. Papa écoute. Parce qu'elle a demandé, papa peut répondre. Aujourd'hui, le pain. Le moulinet attend. Maya hoche la tête. Elle tient la main de papa. Ils achètent le pain. Le pain est chaud. Maya dit merci. Demander à l'adulte, c'est la règle.</t>
+          <t>Le zinc du kiosque claque au soleil. Des journaux sont pincés par une pince. Ça sent l'encre et le bois chaud. Une place de sable brille tout autour. Une ombre de parasol tremble un peu. Papa a un sac de toile à l'épaule. Le kiosque est ouvert ! Oui. On va voir. Amir marche sur le sable chaud. Des grains collent à sa chaussure. En ce moment, Amir s'arrête au bord du zinc. Des sifflets sont dans une boîte. Un sifflet rouge n'est plus là. Il n'y en a plus, le rouge. Il est parti. Il reste le bois. Un sifflet de bois est lisse, clair. Un petit trou rond au bout. Je le veux. Amir tend la main vers la boîte. Papa ne sort pas l'argent. Amir. Tu me demandes ? La main d'Amir s'arrête. Le sifflet reste dans la boîte. Ah. On achète si tu demandes. Tu te souviens ? Je peux demander. Le zinc est chaud sous le soleil. Une pince tient encore un journal. L'encre sent un peu fort.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya marche au marché avec papa. Elle sent le pain chaud. Les étals sont colorés. Elle voit un moulinet. Maya a envie. L'argent se range. Il est dans la poche de papa. Papa est l'adulte. Maya dit : je peux &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Elle demande à papa. Papa écoute. Parce qu'elle a demandé, papa peut répondre. Papa dit : aujourd'hui, le pain. Le moulinet attend. Maya hoche la tête. Elle tient la main de papa. Ils achètent le pain. Le pain est chaud. Maya dit merci. Demander à l'adulte, c'est la règle.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le zinc du kiosque claque au soleil. Des journaux sont pincés par une pince. Ça sent l'encre et le bois chaud. Une place de sable brille tout autour. Une ombre de parasol tremble un peu. Papa a un sac de toile à l'épaule. Le kiosque est ouvert ! Oui. On va voir. Amir marche sur le sable chaud. Des grains collent à sa chaussure. En ce moment, Amir s'arrête au bord du zinc. Des sifflets sont dans une boîte. Un sifflet rouge n'est plus là. Il n'y en a plus, le rouge. Il est parti. Il reste le bois. Un sifflet de bois est lisse, clair. Un petit trou rond au bout. Je le veux. Amir tend la main vers la boîte. Papa ne sort pas l'argent. Amir. Tu me demandes ? La main d'Amir s'arrête. Le sifflet reste dans la boîte. Ah. On achète si tu demandes. Tu te souviens ? Je peux demander. Le zinc est chaud sous le soleil. Une pince tient encore un journal. L'encre sent un peu fort.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,10 +1324,39 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maya marche au marché avec papa. Elle sent le pain chaud. Les étals sont colorés. Elle voit un moulinet. Maya a envie. L'argent se range. Il est dans la poche de papa. Papa est l'adulte.
-enfant-f|Je peux demander. Elle demande à papa. Papa écoute. Parce qu'elle a demandé, papa peut répondre.
-papa|Aujourd'hui, le pain.
-narrateur|Le moulinet attend. Maya hoche la tête. Elle tient la main de papa. Ils achètent le pain. Le pain est chaud. Maya dit merci. Demander à l'adulte, c'est la règle.</t>
+          <t>narrateur|Le zinc du kiosque claque au soleil.
+narrateur|Des journaux sont pincés par une pince.
+narrateur|Ça sent l'encre et le bois chaud.
+narrateur|Une place de sable brille tout autour.
+narrateur|Une ombre de parasol tremble un peu.
+narrateur|Papa a un sac de toile à l'épaule.
+enfant-m|Le kiosque est ouvert !
+papa|Oui.
+papa|On va voir.
+narrateur|Amir marche sur le sable chaud.
+narrateur|Des grains collent à sa chaussure.
+narrateur|En ce moment, Amir s'arrête au bord du zinc.
+narrateur|Des sifflets sont dans une boîte.
+narrateur|Un sifflet rouge n'est plus là.
+enfant-m|Il n'y en a plus, le rouge.
+papa|Il est parti.
+papa|Il reste le bois.
+narrateur|Un sifflet de bois est lisse, clair.
+narrateur|Un petit trou rond au bout.
+enfant-m|Je le veux.
+narrateur|Amir tend la main vers la boîte.
+narrateur|Papa ne sort pas l'argent.
+papa|Amir.
+papa|Tu me demandes ?
+narrateur|La main d'Amir s'arrête.
+narrateur|Le sifflet reste dans la boîte.
+enfant-m|Ah.
+papa|On achète si tu demandes.
+papa|Tu te souviens ?
+enfant-m|Je peux demander.
+narrateur|Le zinc est chaud sous le soleil.
+narrateur|Une pince tient encore un journal.
+narrateur|L'encre sent un peu fort.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1347,12 +1388,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maya veut un moulinet. Que fait-elle ?</t>
+          <t>Amir veut le sifflet de bois. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maya veut un moulinet. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir veut le sifflet de bois. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1367,7 +1408,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>demander | à papa | elle demande | à l'adulte</t>
+          <t>demander | il demande | il demande à papa | à papa | s'il te plaît</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1382,7 +1423,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>L'argent se range. Que fait Maya ?</t>
+          <t>Il demande à papa. Que fait Amir ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1431,7 +1472,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1503,10 +1544,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maya veut un moulinet. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir veut le sifflet de bois.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1531,12 +1572,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya a su demander. Papa, l'adulte, a écouté. L'argent est resté rangé.</t>
+          <t>Papa, s'il te plaît. Je peux avoir le sifflet ? Oui. Merci, Amir. Tu as demandé. Papa sort une pièce de sa poche. La pièce cliquette sur le zinc. On lui tend le sifflet de bois. Amir le prend. Le bois est chaud, tout lisse. Il est à moi. Oui. Parce que tu as demandé. Tu souffles tout doux ? Amir souffle. Le sifflet fait un petit cri clair. Il chante ! Bravo. Un second souffle, plus doux. Le cri est plus petit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya a su &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Papa, l'adulte, a écouté. L'argent est resté rangé.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa, s'il te plaît. Je peux avoir le sifflet ? Oui. Merci, Amir. Tu as demandé. Papa sort une pièce de sa poche. La pièce cliquette sur le zinc. On lui tend le sifflet de bois. Amir le prend. Le bois est chaud, tout lisse. Il est à moi. Oui. Parce que tu as demandé. Tu souffles tout doux ? Amir souffle. Le sifflet fait un petit cri clair. Il chante ! Bravo. Un second souffle, plus doux. Le cri est plus petit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1599,7 +1640,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1675,10 +1716,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maya a su demander. Papa, l'adulte, a écouté. L'argent est resté rangé.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>enfant-m|Papa, s'il te plaît.
+enfant-m|Je peux avoir le sifflet ?
+papa|Oui.
+papa|Merci, Amir.
+papa|Tu as demandé.
+narrateur|Papa sort une pièce de sa poche.
+narrateur|La pièce cliquette sur le zinc.
+narrateur|On lui tend le sifflet de bois.
+narrateur|Amir le prend.
+narrateur|Le bois est chaud, tout lisse.
+enfant-m|Il est à moi.
+papa|Oui.
+papa|Parce que tu as demandé.
+papa|Tu souffles tout doux ?
+narrateur|Amir souffle.
+narrateur|Le sifflet fait un petit cri clair.
+enfant-m|Il chante !
+papa|Bravo.
+narrateur|Un second souffle, plus doux.
+narrateur|Le cri est plus petit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1703,12 +1762,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maya porte le pain. Papa tient sa main. Ils rentrent.</t>
+          <t>Ils quittent le kiosque. Le zinc claque encore un peu. Amir tient le sifflet dans la main. L'autre main tient papa. Tu le mets dans ta poche ? Pas encore. Il est tiède. La place sent le sable chaud. Un pigeon picore près d'une feuille. On rentre. Avec le sifflet. Amir souffle encore, tout bas. Le cri se perd dans le sable.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya porte le pain. Papa tient sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils quittent le kiosque. Le zinc claque encore un peu. Amir tient le sifflet dans la main. L'autre main tient papa. Tu le mets dans ta poche ? Pas encore. Il est tiède. La place sent le sable chaud. Un pigeon picore près d'une feuille. On rentre. Avec le sifflet. Amir souffle encore, tout bas. Le cri se perd dans le sable.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1771,7 +1830,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1843,10 +1902,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maya porte le pain. Papa tient sa main. Ils rentrent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils quittent le kiosque.
+narrateur|Le zinc claque encore un peu.
+narrateur|Amir tient le sifflet dans la main.
+narrateur|L'autre main tient papa.
+papa|Tu le mets dans ta poche ?
+enfant-m|Pas encore.
+enfant-m|Il est tiède.
+narrateur|La place sent le sable chaud.
+narrateur|Un pigeon picore près d'une feuille.
+papa|On rentre.
+enfant-m|Avec le sifflet.
+narrateur|Amir souffle encore, tout bas.
+narrateur|Le cri se perd dans le sable.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1871,12 +1941,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Devant la maison, Amir souffle encore. Le cri est petit, tout rond. Tu l'as dans les mains. Oui. Amir glisse le bois dans sa poche. La poche est chaude contre sa jambe. Il pose la main dessus, pour garder le chant. Le sifflet de bois reste tiède dans sa poche.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Devant la maison, Amir souffle encore. Le cri est petit, tout rond. Tu l'as dans les mains. Oui. Amir glisse le bois dans sa poche. La poche est chaude contre sa jambe. Il pose la main dessus, pour garder le chant. Le sifflet de bois reste tiède dans sa poche.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1932,14 +2002,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2011,10 +2081,16 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Devant la maison, Amir souffle encore.
+narrateur|Le cri est petit, tout rond.
+papa|Tu l'as dans les mains.
+enfant-m|Oui.
+narrateur|Amir glisse le bois dans sa poche.
+narrateur|La poche est chaude contre sa jambe.
+narrateur|Il pose la main dessus, pour garder le chant.
+narrateur|Le sifflet de bois reste tiède dans sa poche.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2147,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-02.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marché</t>
+          <t>kiosque de zinc sur la place, après le soleil</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maya, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
